--- a/data/file_generation/reference/data_187/对比结果_PP01 埋点测试最终处理的只保留 dataID&eventname_-_副本_20260202_024417_res.xlsx
+++ b/data/file_generation/reference/data_187/对比结果_PP01 埋点测试最终处理的只保留 dataID&eventname_-_副本_20260202_024417_res.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liyanjie1/Desktop/program/data_clean-20260204/cleaned_data/output/data_187/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDBD776-3880-D74F-A7A7-4042A25C3D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDD0081-74A9-E348-92E0-27945983758C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="22140" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,9 +94,6 @@
     <t>03000102010000000000000000400003</t>
   </si>
   <si>
-    <t>2025-09-19 11:39:18.359</t>
-  </si>
-  <si>
     <t>pcenter</t>
   </si>
   <si>
@@ -109,10 +106,15 @@
     <t>eventname</t>
   </si>
   <si>
-    <t>Hu_Login_Type</t>
-  </si>
-  <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>20**-**-** **:**:**</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -572,7 +574,7 @@
         <v>500</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G2">
         <v>22872370003264</v>
@@ -581,10 +583,10 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
         <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
       </c>
       <c r="K2">
         <v>65536</v>
@@ -593,34 +595,34 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" t="s">
         <v>28</v>
-      </c>
-      <c r="U2" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -793,13 +795,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE1E6370-89E0-496B-978B-A048F8F5BA93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E94DAA2-2A0D-4BC1-B0AD-4ECAE81AA462}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40D06945-13C6-4546-BC5D-4095CB019998}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1902F7D3-D2DB-47DA-A7E7-25F8C55CAEAC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F1BFE2-1E31-4F9B-8570-E49261D9A9F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7266E26-0C56-4597-8E3C-BFAFB558F37A}"/>
 </file>